--- a/03_Coding_Sheets/383_384_385_387_389.xlsx
+++ b/03_Coding_Sheets/383_384_385_387_389.xlsx
@@ -6309,7 +6309,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1 = No effect size of interest</t>
+          <t>6 = Duplicate / retracted</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>The study uses an identical sample (N=170 product managers from Fortune 500 consumer packaged goods industries) and reports the exact same correlation values as Paper [383] (Lysonski, 1985 in Journal of Marketing). Sliced duplicate publication cited directly in Endnote 6 (p. 26). Excluded under Code 6 (Duplicate) to prevent double counting in meta-analysis. Verbatim Evidence: [p. 18] "Questionnaires were mailed to 449 product managers in consumer packaged goods industries, drawn from the Fortune 500.6 The sampled industries included food, proprietary drugs and cosmetics, soaps, cleansers and allied products, soft drinks, tobacco, paper, and liquor. All of these industries have been using product managers for many years. The final usable sample was 170 completed questionnaires." [p. 26] "6. Lysonski, S., 'A Boundary Theory Investigation of the Product Manager's Role,' Journal of Marketing, 49, (1985), 26-40."</t>
         </is>
       </c>
     </row>
@@ -6332,6 +6337,11 @@
           <t>3 = Non-individual level (team/firm/org analysis)</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Data collected from individual respondents were aggregated to the team level of analysis (N = 23 teams) to examine hypotheses regarding team-level outcomes; no individual-level correlation matrix is reported. Verbatim Evidence: [p. 4] "The final sample consisted of 83 team members and team managers from 23 teams located in the United States and India." [p. 48] "Data collected from individual respondents were aggregated to the team level of analysis (N = 23 teams) to examine the hypotheses regarding team-level outcomes."</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6352,6 +6362,11 @@
           <t>1 = No effect size of interest</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Boundary spanning was operationalized solely as generative AI tool usage (querying ChatGPT and AI tools for external information acquisition) rather than interpersonal or cross-unit boundary spanning. Table 4 reports PLS-SEM latent correlations but lacks zero-order Pearson correlations and descriptive statistics (Mean/SD). Excluded under Code 1 per AI Tool Interaction trap. Verbatim Evidence: [Table 2, p. 7] "I use AI tools to solicit information and resources from external channels." "I make use of external resources through AI tools to support my work." "I actively use AI tools to solicit external work resources." "My work depends upon information and resources actively solicited through AI tools, that is, information and resources beyond those coming through official channels."</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6370,6 +6385,11 @@
       <c r="F47" t="inlineStr">
         <is>
           <t>3 = Non-individual level (team/firm/org analysis)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>The focal unit of statistical analysis is collaborative project teams (N = 452). Survey items use the team as the grammatical referent, violating the individual worker analysis requirement. Verbatim Evidence: [p. 62] "The unit of analysis for this study is the collaborative project team (N = 452 project teams across engineering and construction sectors)." [p. 67] "All survey items were worded with the team as the referent, for example, 'The team actively reaches out to external stakeholders to coordinate project delivery.'"</t>
         </is>
       </c>
     </row>

--- a/03_Coding_Sheets/383_384_385_387_389.xlsx
+++ b/03_Coding_Sheets/383_384_385_387_389.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH4" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Role Conflict, Raw: .28ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Role Conflict, Raw: .28ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH5" t="n">
@@ -946,7 +946,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Person-role conflict, Raw: .18ᵇ | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Person-role conflict, Raw: .18ᵇ | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH6" t="n">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Intersender conflict, Raw: .30ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Intersender conflict, Raw: .30ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH7" t="n">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Intrasender conflict, Raw: .22ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Intrasender conflict, Raw: .22ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH8" t="n">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Role-overload conflict, Raw: .11 | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Role-overload conflict, Raw: .11 | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Role Ambiguity, Raw: .00 | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 4 (p. 34), Row: Aggregate boundary spanning, Col: Role Ambiguity, Raw: .00 | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH10" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH11" t="n">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH12" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH13" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH14" t="n">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH15" t="n">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH16" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH17" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH18" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH19" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH20" t="n">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH21" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH22" t="n">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH23" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH24" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH25" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH26" t="n">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH27" t="n">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH28" t="n">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH29" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatibility between expectations of product manager and role expectations (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH30" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations across multiple role senders (4 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH31" t="n">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring incompatible expectations from a single role sender (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH32" t="n">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman 1970; subscale reliability not reported in Table 1).</t>
+          <t>Sub-dimension of role conflict measuring responsibilities exceeding available time and resources (2 items from Rizzo, House, and Lirtzman (1970); subscale reliability not reported in Table 1).</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH33" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH34" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Table 2 (p. 33), Row: Aggregate boundary spanning, Col: Perceived, Raw: .11ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 2 (p. 33), Row: Aggregate boundary spanning, Col: Perceived, Raw: .11ª | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Aggregate boundary spanning composite combining internal, external, formal, informal, and selected boundary spanning activities (Table 1 footnote a: "This does not add to 19 since some of the subscales overlap").</t>
         </is>
       </c>
       <c r="AH35" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
+          <t>[Methodology, p. 30] "The objective method to quantify environmental uncertainty used six structured items: sales and price volatility of the product class, intensity of brand competition, brand switching, advertising activity, delay in feedback of product line decision after implementation, and market share fluctuations." Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Table 2 (p. 33), Row: Aggregate boundary spanning, Col: Objective, Raw: -.02 | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions: internal boundary spanning... external boundary spanning... Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
+          <t>Table 2 (p. 33), Row: Aggregate boundary spanning, Col: Objective, Raw: -.02 | Global composite: [Methodology, p. 30] "Aggregate boundary spanning was measured with the following dimensions (these components are examined separately in the analysis): internal boundary spanning: internal verbal and written communication; external boundary spanning: external verbal and written communication, e.g., customers, suppliers, trade, consultants; formal boundary spanning: formal meetings and formal written communication occurring, e.g., reports or data from others; informal boundary spanning: informal face-to-face or telephone conversations or informal written communication, e.g., informal notes, memos, and the like; selected aspects: includes travel and coordinating activities. Product managers reported the frequencies of these boundary activities on continuous scales excluding strictly social contacts."</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH36" t="n">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring informal face-to-face or telephone conversations or informal written communication (e.g., informal notes, memos) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH37" t="n">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
+          <t>[Methodology, p. 30] "The objective method to quantify environmental uncertainty used six structured items: sales and price volatility of the product class, intensity of brand competition, brand switching, advertising activity, delay in feedback of product line decision after implementation, and market share fluctuations." Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH38" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Sub-dimension of boundary spanning measuring formal meetings and formal written communication occurring (e.g., reports or data from others) beyond the product manager's department (4 items).</t>
         </is>
       </c>
       <c r="AH39" t="n">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
+          <t>[Methodology, p. 30] "The objective method to quantify environmental uncertainty used six structured items: sales and price volatility of the product class, intensity of brand competition, brand switching, advertising activity, delay in feedback of product line decision after implementation, and market share fluctuations." Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH40" t="n">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." Internal boundary spanning facet measuring internal verbal and written communication beyond the product manager's department (e.g., finance, production, R&amp;D per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH41" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
+          <t>[Methodology, p. 30] "The objective method to quantify environmental uncertainty used six structured items: sales and price volatility of the product class, intensity of brand competition, brand switching, advertising activity, delay in feedback of product line decision after implementation, and market share fluctuations." Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH42" t="n">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
+          <t>[Methodology, p. 30] "Boundary spanning, defined as communication beyond a product manager's department, was measured by refining an instrument developed by Aiken and Hage (1972) and used by Leifer (1975)." External boundary spanning facet measuring external verbal and written communication (e.g., customers, suppliers, the trade, consultants per Rule 28; 4 items).</t>
         </is>
       </c>
       <c r="AH43" t="n">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
+          <t>[Methodology, p. 30] "The objective method to quantify environmental uncertainty used six structured items: sales and price volatility of the product class, intensity of brand competition, brand switching, advertising activity, delay in feedback of product line decision after implementation, and market share fluctuations." Objective environmental uncertainty measuring market volatility across product class and competitors (7 items reported in Table 1; alpha 0.48).</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6312,11 +6312,6 @@
           <t>6 = Duplicate / retracted</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>The study uses an identical sample (N=170 product managers from Fortune 500 consumer packaged goods industries) and reports the exact same correlation values as Paper [383] (Lysonski, 1985 in Journal of Marketing). Sliced duplicate publication cited directly in Endnote 6 (p. 26). Excluded under Code 6 (Duplicate) to prevent double counting in meta-analysis. Verbatim Evidence: [p. 18] "Questionnaires were mailed to 449 product managers in consumer packaged goods industries, drawn from the Fortune 500.6 The sampled industries included food, proprietary drugs and cosmetics, soaps, cleansers and allied products, soft drinks, tobacco, paper, and liquor. All of these industries have been using product managers for many years. The final usable sample was 170 completed questionnaires." [p. 26] "6. Lysonski, S., 'A Boundary Theory Investigation of the Product Manager's Role,' Journal of Marketing, 49, (1985), 26-40."</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6337,11 +6332,6 @@
           <t>3 = Non-individual level (team/firm/org analysis)</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Data collected from individual respondents were aggregated to the team level of analysis (N = 23 teams) to examine hypotheses regarding team-level outcomes; no individual-level correlation matrix is reported. Verbatim Evidence: [p. 4] "The final sample consisted of 83 team members and team managers from 23 teams located in the United States and India." [p. 48] "Data collected from individual respondents were aggregated to the team level of analysis (N = 23 teams) to examine the hypotheses regarding team-level outcomes."</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6362,11 +6352,6 @@
           <t>1 = No effect size of interest</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Boundary spanning was operationalized solely as generative AI tool usage (querying ChatGPT and AI tools for external information acquisition) rather than interpersonal or cross-unit boundary spanning. Table 4 reports PLS-SEM latent correlations but lacks zero-order Pearson correlations and descriptive statistics (Mean/SD). Excluded under Code 1 per AI Tool Interaction trap. Verbatim Evidence: [Table 2, p. 7] "I use AI tools to solicit information and resources from external channels." "I make use of external resources through AI tools to support my work." "I actively use AI tools to solicit external work resources." "My work depends upon information and resources actively solicited through AI tools, that is, information and resources beyond those coming through official channels."</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6385,11 +6370,6 @@
       <c r="F47" t="inlineStr">
         <is>
           <t>3 = Non-individual level (team/firm/org analysis)</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>The focal unit of statistical analysis is collaborative project teams (N = 452). Survey items use the team as the grammatical referent, violating the individual worker analysis requirement. Verbatim Evidence: [p. 62] "The unit of analysis for this study is the collaborative project team (N = 452 project teams across engineering and construction sectors)." [p. 67] "All survey items were worded with the team as the referent, for example, 'The team actively reaches out to external stakeholders to coordinate project delivery.'"</t>
         </is>
       </c>
     </row>
